--- a/www/terminologies/ValueSet-JDV-J18-EquipementSpecifique-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J18-EquipementSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="357">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1027,6 +1027,54 @@
   </si>
   <si>
     <t>Espace de consommation de drogues à fumer</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>Appareil de thermoformage</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>Appareil de thermosoudage</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>Plateforme de force (étude de la posture)</t>
+  </si>
+  <si>
+    <t>239</t>
+  </si>
+  <si>
+    <t>Plateforme de pression (étude de la marche)</t>
+  </si>
+  <si>
+    <t>240</t>
+  </si>
+  <si>
+    <t>Piste de marche</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>Tapis de course</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>Système vidéo d'analyse de la marche et de la course</t>
+  </si>
+  <si>
+    <t>243</t>
+  </si>
+  <si>
+    <t>Semelles avec capteurs embarqués</t>
   </si>
   <si>
     <t/>
@@ -1297,7 +1345,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B158"/>
+  <dimension ref="A1:B166"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2557,15 +2605,79 @@
         <v>338</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>356</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J18-EquipementSpecifique-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J18-EquipementSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="379">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260601120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -168,7 +168,7 @@
     <t>054</t>
   </si>
   <si>
-    <t>IRM corps entier</t>
+    <t>Imagerie par Résonance Magnétique (IRM) corps entier</t>
   </si>
   <si>
     <t>064</t>
@@ -234,7 +234,7 @@
     <t>087</t>
   </si>
   <si>
-    <t>IRM à champ ouvert</t>
+    <t>Imagerie par Résonance Magnétique (IRM) à champ ouvert</t>
   </si>
   <si>
     <t>088</t>
@@ -966,7 +966,7 @@
     <t>221</t>
   </si>
   <si>
-    <t>IRM obésité - bariatrique</t>
+    <t>Imagerie par Résonance Magnétique (IRM) obésité – bariatrique</t>
   </si>
   <si>
     <t>222</t>
@@ -1075,6 +1075,72 @@
   </si>
   <si>
     <t>Semelles avec capteurs embarqués</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>Échographe polyvalent</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>Imagerie par Résonance Magnétique (IRM) à champ fermé (ou tunnel)</t>
+  </si>
+  <si>
+    <t>248</t>
+  </si>
+  <si>
+    <t>Imagerie par Résonance Magnétique (IRM) pédiatrique (compatible anesthésie)</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>Radiologie numérique standard</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>Scanner base dose (LDCT)</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>Plateau réfraction - Pachymétrie</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>Rétinographe</t>
+  </si>
+  <si>
+    <t>253</t>
+  </si>
+  <si>
+    <t>Oculomètre certifié (C2)</t>
+  </si>
+  <si>
+    <t>254</t>
+  </si>
+  <si>
+    <t>Coordimètre</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>Tests scorés et/ou normés en neurovision</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>Accompagnement à l’essai de fauteuil roulant</t>
   </si>
   <si>
     <t/>
@@ -1345,7 +1411,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B166"/>
+  <dimension ref="A1:B177"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2669,15 +2735,103 @@
         <v>354</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>378</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J18-EquipementSpecifique-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J18-EquipementSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="357">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -168,7 +168,7 @@
     <t>054</t>
   </si>
   <si>
-    <t>Imagerie par Résonance Magnétique (IRM) corps entier</t>
+    <t>IRM corps entier</t>
   </si>
   <si>
     <t>064</t>
@@ -234,7 +234,7 @@
     <t>087</t>
   </si>
   <si>
-    <t>Imagerie par Résonance Magnétique (IRM) à champ ouvert</t>
+    <t>IRM à champ ouvert</t>
   </si>
   <si>
     <t>088</t>
@@ -966,7 +966,7 @@
     <t>221</t>
   </si>
   <si>
-    <t>Imagerie par Résonance Magnétique (IRM) obésité – bariatrique</t>
+    <t>IRM obésité - bariatrique</t>
   </si>
   <si>
     <t>222</t>
@@ -1075,72 +1075,6 @@
   </si>
   <si>
     <t>Semelles avec capteurs embarqués</t>
-  </si>
-  <si>
-    <t>246</t>
-  </si>
-  <si>
-    <t>Échographe polyvalent</t>
-  </si>
-  <si>
-    <t>247</t>
-  </si>
-  <si>
-    <t>Imagerie par Résonance Magnétique (IRM) à champ fermé (ou tunnel)</t>
-  </si>
-  <si>
-    <t>248</t>
-  </si>
-  <si>
-    <t>Imagerie par Résonance Magnétique (IRM) pédiatrique (compatible anesthésie)</t>
-  </si>
-  <si>
-    <t>249</t>
-  </si>
-  <si>
-    <t>Radiologie numérique standard</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>Scanner base dose (LDCT)</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>Plateau réfraction - Pachymétrie</t>
-  </si>
-  <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>Rétinographe</t>
-  </si>
-  <si>
-    <t>253</t>
-  </si>
-  <si>
-    <t>Oculomètre certifié (C2)</t>
-  </si>
-  <si>
-    <t>254</t>
-  </si>
-  <si>
-    <t>Coordimètre</t>
-  </si>
-  <si>
-    <t>255</t>
-  </si>
-  <si>
-    <t>Tests scorés et/ou normés en neurovision</t>
-  </si>
-  <si>
-    <t>256</t>
-  </si>
-  <si>
-    <t>Accompagnement à l’essai de fauteuil roulant</t>
   </si>
   <si>
     <t/>
@@ -1411,7 +1345,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B177"/>
+  <dimension ref="A1:B166"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2735,103 +2669,15 @@
         <v>354</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B166" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="B166" t="s" s="2">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="B167" t="s" s="2">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="B169" t="s" s="2">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="B170" t="s" s="2">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="B171" t="s" s="2">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="B172" t="s" s="2">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="B173" t="s" s="2">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="B174" t="s" s="2">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>378</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J18-EquipementSpecifique-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J18-EquipementSpecifique-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -204,7 +204,7 @@
     <t>072</t>
   </si>
   <si>
-    <t>Table de bloc opératoire obésité (poids supérieur à 250 kg) - bariatrique</t>
+    <t>Table de bloc opératoire obésité (poids &gt; 250 kg) - bariatrique</t>
   </si>
   <si>
     <t>083</t>
